--- a/src/experimentation/experiment_results/centralized/results.xlsx
+++ b/src/experimentation/experiment_results/centralized/results.xlsx
@@ -545,37 +545,37 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>216</v>
+        <v>93</v>
       </c>
       <c r="H2">
-        <v>248</v>
+        <v>5000</v>
       </c>
       <c r="I2">
-        <v>248</v>
+        <v>5000</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>177.5064</v>
+        <v>4561.122400000259</v>
       </c>
       <c r="N2">
-        <v>0.7157516129032259</v>
+        <v>0.9122244800000519</v>
       </c>
       <c r="O2">
-        <v>177.3999999999996</v>
+        <v>4958.733333333334</v>
       </c>
       <c r="P2">
-        <v>0.7153225806451597</v>
+        <v>0.9917466666666667</v>
       </c>
       <c r="Q2">
-        <v>99.96000000000001</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -592,37 +592,37 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>222</v>
+        <v>93</v>
       </c>
       <c r="H3">
-        <v>266</v>
+        <v>5000</v>
       </c>
       <c r="I3">
-        <v>266</v>
+        <v>5000</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>187.5151999999999</v>
+        <v>4561.122400000259</v>
       </c>
       <c r="N3">
-        <v>0.7049443609022553</v>
+        <v>0.9122244800000519</v>
       </c>
       <c r="O3">
-        <v>195.3333333333335</v>
+        <v>4958.733333333334</v>
       </c>
       <c r="P3">
-        <v>0.734335839598998</v>
+        <v>0.9917466666666667</v>
       </c>
       <c r="Q3">
-        <v>99.96000000000001</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -639,37 +639,37 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>211</v>
+        <v>93</v>
       </c>
       <c r="H4">
-        <v>264</v>
+        <v>5000</v>
       </c>
       <c r="I4">
-        <v>264</v>
+        <v>5000</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>185.7143999999999</v>
+        <v>4561.122400000259</v>
       </c>
       <c r="N4">
-        <v>0.7034636363636361</v>
+        <v>0.9122244800000519</v>
       </c>
       <c r="O4">
-        <v>180.0000000000001</v>
+        <v>4958.733333333334</v>
       </c>
       <c r="P4">
-        <v>0.6818181818181821</v>
+        <v>0.9917466666666667</v>
       </c>
       <c r="Q4">
-        <v>99.96000000000001</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -686,37 +686,37 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>231</v>
+        <v>93</v>
       </c>
       <c r="H5">
-        <v>270</v>
+        <v>5000</v>
       </c>
       <c r="I5">
-        <v>270</v>
+        <v>5000</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>200.8671999999999</v>
+        <v>4561.122400000259</v>
       </c>
       <c r="N5">
-        <v>0.7439525925925923</v>
+        <v>0.9122244800000519</v>
       </c>
       <c r="O5">
-        <v>190.6666666666667</v>
+        <v>4958.733333333334</v>
       </c>
       <c r="P5">
-        <v>0.7061728395061732</v>
+        <v>0.9917466666666667</v>
       </c>
       <c r="Q5">
-        <v>99.96000000000001</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -733,37 +733,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>206</v>
+        <v>93</v>
       </c>
       <c r="H6">
-        <v>246</v>
+        <v>5000</v>
       </c>
       <c r="I6">
-        <v>246</v>
+        <v>5000</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>175.1944</v>
+        <v>4561.122400000259</v>
       </c>
       <c r="N6">
-        <v>0.7121723577235773</v>
+        <v>0.9122244800000519</v>
       </c>
       <c r="O6">
-        <v>182.1999999999999</v>
+        <v>4958.733333333334</v>
       </c>
       <c r="P6">
-        <v>0.7406504065040646</v>
+        <v>0.9917466666666667</v>
       </c>
       <c r="Q6">
-        <v>99.96000000000001</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -780,37 +780,37 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>437</v>
+        <v>203</v>
       </c>
       <c r="H7">
-        <v>553</v>
+        <v>10000</v>
       </c>
       <c r="I7">
-        <v>553</v>
+        <v>10000</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>382.0539999999997</v>
+        <v>9511.315999999086</v>
       </c>
       <c r="N7">
-        <v>0.6908752260397826</v>
+        <v>0.9511315999999086</v>
       </c>
       <c r="O7">
-        <v>338.699999999999</v>
+        <v>9913.549999999999</v>
       </c>
       <c r="P7">
-        <v>0.612477396021698</v>
+        <v>0.9913549999999999</v>
       </c>
       <c r="Q7">
-        <v>99.98999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -827,37 +827,37 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>516</v>
+        <v>203</v>
       </c>
       <c r="H8">
-        <v>540</v>
+        <v>10000</v>
       </c>
       <c r="I8">
-        <v>540</v>
+        <v>10000</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>372.4044000000001</v>
+        <v>9511.315999999086</v>
       </c>
       <c r="N8">
-        <v>0.689637777777778</v>
+        <v>0.9511315999999086</v>
       </c>
       <c r="O8">
-        <v>351.9999999999979</v>
+        <v>9913.549999999999</v>
       </c>
       <c r="P8">
-        <v>0.6518518518518479</v>
+        <v>0.9913549999999999</v>
       </c>
       <c r="Q8">
-        <v>99.98999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -874,37 +874,37 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>443</v>
+        <v>203</v>
       </c>
       <c r="H9">
-        <v>584</v>
+        <v>10000</v>
       </c>
       <c r="I9">
-        <v>584</v>
+        <v>10000</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>415.3158000000007</v>
+        <v>9511.315999999086</v>
       </c>
       <c r="N9">
-        <v>0.7111571917808232</v>
+        <v>0.9511315999999086</v>
       </c>
       <c r="O9">
-        <v>378.8499999999995</v>
+        <v>9913.549999999999</v>
       </c>
       <c r="P9">
-        <v>0.6487157534246566</v>
+        <v>0.9913549999999999</v>
       </c>
       <c r="Q9">
-        <v>99.98999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -921,37 +921,37 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>498</v>
+        <v>203</v>
       </c>
       <c r="H10">
-        <v>504</v>
+        <v>10000</v>
       </c>
       <c r="I10">
-        <v>504</v>
+        <v>10000</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>338.9127999999995</v>
+        <v>9511.315999999086</v>
       </c>
       <c r="N10">
-        <v>0.6724460317460309</v>
+        <v>0.9511315999999086</v>
       </c>
       <c r="O10">
-        <v>302.4999999999987</v>
+        <v>9913.549999999999</v>
       </c>
       <c r="P10">
-        <v>0.6001984126984102</v>
+        <v>0.9913549999999999</v>
       </c>
       <c r="Q10">
-        <v>99.98999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -968,37 +968,37 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>499</v>
+        <v>203</v>
       </c>
       <c r="H11">
-        <v>551</v>
+        <v>10000</v>
       </c>
       <c r="I11">
-        <v>551</v>
+        <v>10000</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>383.6323999999998</v>
+        <v>9511.315999999086</v>
       </c>
       <c r="N11">
-        <v>0.6962475499092555</v>
+        <v>0.9511315999999086</v>
       </c>
       <c r="O11">
-        <v>424.4999999999981</v>
+        <v>9913.549999999999</v>
       </c>
       <c r="P11">
-        <v>0.7704174228675102</v>
+        <v>0.9913549999999999</v>
       </c>
       <c r="Q11">
-        <v>99.98999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1015,37 +1015,37 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>832</v>
+        <v>309</v>
       </c>
       <c r="H12">
-        <v>887</v>
+        <v>15000</v>
       </c>
       <c r="I12">
-        <v>887</v>
+        <v>15000</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>599.66808888889</v>
+        <v>14466.56915555591</v>
       </c>
       <c r="N12">
-        <v>0.6760632343730439</v>
+        <v>0.9644379437037272</v>
       </c>
       <c r="O12">
-        <v>572.0285714285721</v>
+        <v>14866.37142857143</v>
       </c>
       <c r="P12">
-        <v>0.6449025607988412</v>
+        <v>0.9910914285714284</v>
       </c>
       <c r="Q12">
-        <v>99.99555555555555</v>
+        <v>97.33333333333334</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1062,37 +1062,37 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>872</v>
+        <v>309</v>
       </c>
       <c r="H13">
-        <v>983</v>
+        <v>15000</v>
       </c>
       <c r="I13">
-        <v>983</v>
+        <v>15000</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>714.85671111111</v>
+        <v>14466.56915555591</v>
       </c>
       <c r="N13">
-        <v>0.7272194416186267</v>
+        <v>0.9644379437037272</v>
       </c>
       <c r="O13">
-        <v>701.8285714285701</v>
+        <v>14866.37142857143</v>
       </c>
       <c r="P13">
-        <v>0.7139659933149237</v>
+        <v>0.9910914285714284</v>
       </c>
       <c r="Q13">
-        <v>99.99555555555555</v>
+        <v>97.33333333333334</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1109,37 +1109,37 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>818</v>
+        <v>309</v>
       </c>
       <c r="H14">
-        <v>824</v>
+        <v>15000</v>
       </c>
       <c r="I14">
-        <v>824</v>
+        <v>15000</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>551.8567111111113</v>
+        <v>14466.56915555591</v>
       </c>
       <c r="N14">
-        <v>0.6697290183387273</v>
+        <v>0.9644379437037272</v>
       </c>
       <c r="O14">
-        <v>538.3714285714261</v>
+        <v>14866.37142857143</v>
       </c>
       <c r="P14">
-        <v>0.6533633841886239</v>
+        <v>0.9910914285714284</v>
       </c>
       <c r="Q14">
-        <v>99.99555555555555</v>
+        <v>97.33333333333334</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1156,37 +1156,37 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>797</v>
+        <v>309</v>
       </c>
       <c r="H15">
-        <v>881</v>
+        <v>15000</v>
       </c>
       <c r="I15">
-        <v>881</v>
+        <v>15000</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>607.3388444444445</v>
+        <v>14466.56915555591</v>
       </c>
       <c r="N15">
-        <v>0.6893743977803002</v>
+        <v>0.9644379437037272</v>
       </c>
       <c r="O15">
-        <v>573.7428571428603</v>
+        <v>14866.37142857143</v>
       </c>
       <c r="P15">
-        <v>0.6512404734879231</v>
+        <v>0.9910914285714284</v>
       </c>
       <c r="Q15">
-        <v>99.99555555555555</v>
+        <v>97.33333333333334</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1203,37 +1203,37 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>684</v>
+        <v>309</v>
       </c>
       <c r="H16">
-        <v>844</v>
+        <v>15000</v>
       </c>
       <c r="I16">
-        <v>844</v>
+        <v>15000</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>558.1835555555551</v>
+        <v>14466.56915555591</v>
       </c>
       <c r="N16">
-        <v>0.6613549236440227</v>
+        <v>0.9644379437037272</v>
       </c>
       <c r="O16">
-        <v>591.4857142857111</v>
+        <v>14866.37142857143</v>
       </c>
       <c r="P16">
-        <v>0.7008124576844919</v>
+        <v>0.9910914285714284</v>
       </c>
       <c r="Q16">
-        <v>99.99555555555555</v>
+        <v>97.33333333333334</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1250,37 +1250,37 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>1111</v>
+        <v>20000</v>
       </c>
       <c r="H17">
-        <v>1145</v>
+        <v>20000</v>
       </c>
       <c r="I17">
-        <v>1145</v>
+        <v>20000</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>776.2970000000008</v>
+        <v>19421.06794999324</v>
       </c>
       <c r="N17">
-        <v>0.6779886462882103</v>
+        <v>0.9710533974996622</v>
       </c>
       <c r="O17">
-        <v>837.6600000000074</v>
+        <v>19433.51999999324</v>
       </c>
       <c r="P17">
-        <v>0.7315807860262074</v>
+        <v>0.971675999999662</v>
       </c>
       <c r="Q17">
-        <v>99.99749999999999</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1297,37 +1297,37 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>1135</v>
+        <v>20000</v>
       </c>
       <c r="H18">
-        <v>1194</v>
+        <v>20000</v>
       </c>
       <c r="I18">
-        <v>1194</v>
+        <v>20000</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>813.7091499999998</v>
+        <v>19421.06794999324</v>
       </c>
       <c r="N18">
-        <v>0.6814984505862645</v>
+        <v>0.9710533974996622</v>
       </c>
       <c r="O18">
-        <v>723.3199999999993</v>
+        <v>19433.51999999324</v>
       </c>
       <c r="P18">
-        <v>0.6057956448911217</v>
+        <v>0.971675999999662</v>
       </c>
       <c r="Q18">
-        <v>99.99749999999999</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1344,37 +1344,37 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>950</v>
+        <v>20000</v>
       </c>
       <c r="H19">
-        <v>1225</v>
+        <v>20000</v>
       </c>
       <c r="I19">
-        <v>1225</v>
+        <v>20000</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>866.15595</v>
+        <v>19421.06794999324</v>
       </c>
       <c r="N19">
-        <v>0.7070660816326531</v>
+        <v>0.9710533974996622</v>
       </c>
       <c r="O19">
-        <v>779.8800000000026</v>
+        <v>19433.51999999324</v>
       </c>
       <c r="P19">
-        <v>0.6366367346938797</v>
+        <v>0.971675999999662</v>
       </c>
       <c r="Q19">
-        <v>99.99749999999999</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1391,37 +1391,37 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>1049</v>
+        <v>20000</v>
       </c>
       <c r="H20">
-        <v>1260</v>
+        <v>20000</v>
       </c>
       <c r="I20">
-        <v>1260</v>
+        <v>20000</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>892.0960500000003</v>
+        <v>19421.06794999324</v>
       </c>
       <c r="N20">
-        <v>0.7080127380952383</v>
+        <v>0.9710533974996622</v>
       </c>
       <c r="O20">
-        <v>908.9999999999964</v>
+        <v>19433.51999999324</v>
       </c>
       <c r="P20">
-        <v>0.7214285714285685</v>
+        <v>0.971675999999662</v>
       </c>
       <c r="Q20">
-        <v>99.99749999999999</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1438,37 +1438,37 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>1020</v>
+        <v>20000</v>
       </c>
       <c r="H21">
-        <v>1165</v>
+        <v>20000</v>
       </c>
       <c r="I21">
-        <v>1165</v>
+        <v>20000</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>786.7430499999989</v>
+        <v>19421.06794999324</v>
       </c>
       <c r="N21">
-        <v>0.6753159227467802</v>
+        <v>0.9710533974996622</v>
       </c>
       <c r="O21">
-        <v>775.3000000000017</v>
+        <v>19433.51999999324</v>
       </c>
       <c r="P21">
-        <v>0.665493562231761</v>
+        <v>0.971675999999662</v>
       </c>
       <c r="Q21">
-        <v>99.99749999999999</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -1485,37 +1485,37 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>1387</v>
+        <v>489</v>
       </c>
       <c r="H22">
-        <v>1540</v>
+        <v>25000</v>
       </c>
       <c r="I22">
-        <v>1540</v>
+        <v>25000</v>
       </c>
       <c r="J22">
         <v>1</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>1067.688543999996</v>
+        <v>24371.64844800757</v>
       </c>
       <c r="N22">
-        <v>0.6933042493506469</v>
+        <v>0.9748659379203028</v>
       </c>
       <c r="O22">
-        <v>1035.533333333338</v>
+        <v>24774.82666666667</v>
       </c>
       <c r="P22">
-        <v>0.6724242424242454</v>
+        <v>0.9909930666666668</v>
       </c>
       <c r="Q22">
-        <v>99.9984</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -1532,37 +1532,37 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1377</v>
+        <v>489</v>
       </c>
       <c r="H23">
-        <v>1593</v>
+        <v>25000</v>
       </c>
       <c r="I23">
-        <v>1593</v>
+        <v>25000</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>1106.115935999996</v>
+        <v>24371.64844800757</v>
       </c>
       <c r="N23">
-        <v>0.6943602862523515</v>
+        <v>0.9748659379203028</v>
       </c>
       <c r="O23">
-        <v>1020.493333333328</v>
+        <v>24774.82666666667</v>
       </c>
       <c r="P23">
-        <v>0.6406110064867095</v>
+        <v>0.9909930666666668</v>
       </c>
       <c r="Q23">
-        <v>99.9984</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -1579,37 +1579,37 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>1258</v>
+        <v>489</v>
       </c>
       <c r="H24">
-        <v>1532</v>
+        <v>25000</v>
       </c>
       <c r="I24">
-        <v>1532</v>
+        <v>25000</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>1050.563936000001</v>
+        <v>24371.64844800757</v>
       </c>
       <c r="N24">
-        <v>0.6857466945169719</v>
+        <v>0.9748659379203028</v>
       </c>
       <c r="O24">
-        <v>1070.253333333334</v>
+        <v>24774.82666666667</v>
       </c>
       <c r="P24">
-        <v>0.698598781549174</v>
+        <v>0.9909930666666668</v>
       </c>
       <c r="Q24">
-        <v>99.9984</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -1626,37 +1626,37 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>1283</v>
+        <v>489</v>
       </c>
       <c r="H25">
-        <v>1589</v>
+        <v>25000</v>
       </c>
       <c r="I25">
-        <v>1589</v>
+        <v>25000</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>1115.020447999998</v>
+        <v>24371.64844800757</v>
       </c>
       <c r="N25">
-        <v>0.7017120503461286</v>
+        <v>0.9748659379203028</v>
       </c>
       <c r="O25">
-        <v>1143.639999999997</v>
+        <v>24774.82666666667</v>
       </c>
       <c r="P25">
-        <v>0.7197230962869713</v>
+        <v>0.9909930666666668</v>
       </c>
       <c r="Q25">
-        <v>99.9984</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -1673,37 +1673,37 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>1392</v>
+        <v>489</v>
       </c>
       <c r="H26">
-        <v>1589</v>
+        <v>25000</v>
       </c>
       <c r="I26">
-        <v>1589</v>
+        <v>25000</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>1114.81344</v>
+        <v>24371.64844800757</v>
       </c>
       <c r="N26">
-        <v>0.7015817747010701</v>
+        <v>0.9748659379203028</v>
       </c>
       <c r="O26">
-        <v>1123.399999999995</v>
+        <v>24774.82666666667</v>
       </c>
       <c r="P26">
-        <v>0.7069855254877251</v>
+        <v>0.9909930666666668</v>
       </c>
       <c r="Q26">
-        <v>99.9984</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1791,37 +1791,37 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>217.2</v>
+        <v>93</v>
       </c>
       <c r="F2">
-        <v>258.8</v>
+        <v>5000</v>
       </c>
       <c r="G2">
-        <v>258.8</v>
+        <v>5000</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>185.3595199999999</v>
+        <v>4561.122400000259</v>
       </c>
       <c r="L2">
-        <v>0.7160569120970574</v>
+        <v>0.912224480000052</v>
       </c>
       <c r="M2">
-        <v>185.1199999999999</v>
+        <v>4958.733333333334</v>
       </c>
       <c r="N2">
-        <v>0.7156599696145155</v>
+        <v>0.9917466666666666</v>
       </c>
       <c r="O2">
-        <v>99.96000000000001</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -1838,37 +1838,37 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>478.6</v>
+        <v>203</v>
       </c>
       <c r="F3">
-        <v>546.4</v>
+        <v>10000</v>
       </c>
       <c r="G3">
-        <v>546.4</v>
+        <v>10000</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>378.46388</v>
+        <v>9511.315999999086</v>
       </c>
       <c r="L3">
-        <v>0.6920727554507341</v>
+        <v>0.9511315999999086</v>
       </c>
       <c r="M3">
-        <v>359.3099999999987</v>
+        <v>9913.549999999999</v>
       </c>
       <c r="N3">
-        <v>0.6567321673728246</v>
+        <v>0.9913549999999999</v>
       </c>
       <c r="O3">
-        <v>99.98999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1885,37 +1885,37 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>800.6</v>
+        <v>309</v>
       </c>
       <c r="F4">
-        <v>883.8</v>
+        <v>15000</v>
       </c>
       <c r="G4">
-        <v>883.8</v>
+        <v>15000</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>606.3807822222223</v>
+        <v>14466.56915555591</v>
       </c>
       <c r="L4">
-        <v>0.6847482031509442</v>
+        <v>0.9644379437037272</v>
       </c>
       <c r="M4">
-        <v>595.4914285714279</v>
+        <v>14866.37142857143</v>
       </c>
       <c r="N4">
-        <v>0.6728569738949608</v>
+        <v>0.9910914285714284</v>
       </c>
       <c r="O4">
-        <v>99.99555555555555</v>
+        <v>97.33333333333334</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1932,37 +1932,37 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>1053</v>
+        <v>20000</v>
       </c>
       <c r="F5">
-        <v>1197.8</v>
+        <v>20000</v>
       </c>
       <c r="G5">
-        <v>1197.8</v>
+        <v>20000</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>827.00024</v>
+        <v>19421.06794999324</v>
       </c>
       <c r="L5">
-        <v>0.6899763678698292</v>
+        <v>0.9710533974996622</v>
       </c>
       <c r="M5">
-        <v>805.0320000000014</v>
+        <v>19433.51999999324</v>
       </c>
       <c r="N5">
-        <v>0.6721870598543076</v>
+        <v>0.971675999999662</v>
       </c>
       <c r="O5">
-        <v>99.99749999999999</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1979,37 +1979,37 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>1339.4</v>
+        <v>489</v>
       </c>
       <c r="F6">
-        <v>1568.6</v>
+        <v>25000</v>
       </c>
       <c r="G6">
-        <v>1568.6</v>
+        <v>25000</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>1090.840460799998</v>
+        <v>24371.64844800757</v>
       </c>
       <c r="L6">
-        <v>0.6953410110334338</v>
+        <v>0.9748659379203028</v>
       </c>
       <c r="M6">
-        <v>1078.663999999999</v>
+        <v>24774.82666666667</v>
       </c>
       <c r="N6">
-        <v>0.6876685304469651</v>
+        <v>0.9909930666666668</v>
       </c>
       <c r="O6">
-        <v>99.9984</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
   </sheetData>
